--- a/content/xls/NSO_p_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_p_regions_01.07.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485D8FDA-D275-421D-A64C-00ADBE7338D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500AE383-CE7B-4BF8-B672-AD079BB6F532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -1347,7 +1347,7 @@
         <v>0.18</v>
       </c>
       <c r="D12" s="3">
-        <v>2.5</v>
+        <v>-2.5</v>
       </c>
       <c r="E12" s="2">
         <v>0.79500000000000004</v>
@@ -1459,7 +1459,7 @@
         <v>0.13000000000000003</v>
       </c>
       <c r="D14" s="3">
-        <v>2.7000000000000024</v>
+        <v>-2.7</v>
       </c>
       <c r="E14" s="2">
         <v>0.84299999999999997</v>
@@ -1515,7 +1515,7 @@
         <v>0.159</v>
       </c>
       <c r="D15" s="3">
-        <v>3.5</v>
+        <v>-3.5</v>
       </c>
       <c r="E15" s="2">
         <v>0.80600000000000005</v>
@@ -1683,7 +1683,7 @@
         <v>0.13600000000000004</v>
       </c>
       <c r="D18" s="3">
-        <v>2.0000000000000018</v>
+        <v>-2</v>
       </c>
       <c r="E18" s="2">
         <v>0.84399999999999997</v>
@@ -2019,7 +2019,7 @@
         <v>0.28099999999999997</v>
       </c>
       <c r="D24" s="3">
-        <v>3.6999999999999922</v>
+        <v>-3.7</v>
       </c>
       <c r="E24" s="2">
         <v>0.68200000000000005</v>

--- a/content/xls/NSO_p_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_p_regions_01.07.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500AE383-CE7B-4BF8-B672-AD079BB6F532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837DE66C-3432-4011-8E5E-31F82F398D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -169,9 +169,6 @@
     <t>Количество точек финансового доступа, ед.</t>
   </si>
   <si>
-    <t>Количество Финансовых помощников, ед.</t>
-  </si>
-  <si>
     <t>Количество торговых точек с сервисом "Выдача наличных на кассе", ед.</t>
   </si>
   <si>
@@ -182,6 +179,9 @@
   </si>
   <si>
     <t>Количество банкоматов, ед.</t>
+  </si>
+  <si>
+    <t>Количество финансовых помощников, ед.</t>
   </si>
 </sst>
 </file>
@@ -746,31 +746,31 @@
         <v>33</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>34</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L1" s="13" t="s">
         <v>35</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>38</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P1" s="13" t="s">
         <v>37</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R1" s="10" t="s">
         <v>36</v>

--- a/content/xls/NSO_p_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_p_regions_01.07.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837DE66C-3432-4011-8E5E-31F82F398D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EE6535-41D8-40F2-AEDC-48397D482BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -284,9 +284,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -315,12 +312,25 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color theme="9" tint="-0.499984740745262"/>
@@ -720,64 +730,64 @@
     <col min="19" max="19" width="9.109375" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="7" customFormat="1" ht="118.15" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:18" s="6" customFormat="1" ht="118.15" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1">
@@ -786,54 +796,54 @@
       <c r="C2" s="2">
         <v>0.21199999999999997</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="13">
         <v>0</v>
       </c>
       <c r="E2" s="2">
         <v>0.78800000000000003</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <v>11.7</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
-        <v>1</v>
-      </c>
-      <c r="L2" s="8">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4">
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1</v>
+      </c>
+      <c r="L2" s="7">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
         <v>3</v>
       </c>
-      <c r="N2" s="8">
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3">
         <v>12</v>
       </c>
-      <c r="P2" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3">
         <v>9</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1">
@@ -842,54 +852,54 @@
       <c r="C3" s="2">
         <v>0.24399999999999999</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="13">
         <v>0</v>
       </c>
       <c r="E3" s="2">
         <v>0.75600000000000001</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>9.2999999999999972</v>
       </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
         <v>4</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="7">
         <v>-1</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="3">
         <v>5</v>
       </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
+      <c r="N3" s="7">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
         <v>21</v>
       </c>
-      <c r="P3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>1</v>
-      </c>
-      <c r="R3" s="8">
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1</v>
+      </c>
+      <c r="R3" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1">
@@ -898,54 +908,54 @@
       <c r="C4" s="2">
         <v>0.18400000000000005</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="13">
         <v>0</v>
       </c>
       <c r="E4" s="2">
         <v>0.81599999999999995</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>0.20000000000000018</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="8">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="8">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="7">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
         <v>17</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4" s="7">
         <v>-3</v>
       </c>
-      <c r="Q4" s="4">
-        <v>1</v>
-      </c>
-      <c r="R4" s="8">
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1">
@@ -954,54 +964,54 @@
       <c r="C5" s="2">
         <v>0.16700000000000004</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="13">
         <v>0</v>
       </c>
       <c r="E5" s="2">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>9.3999999999999968</v>
       </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4">
-        <v>1</v>
-      </c>
-      <c r="L5" s="8">
-        <v>1</v>
-      </c>
-      <c r="M5" s="4">
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3">
         <v>6</v>
       </c>
-      <c r="N5" s="8">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
         <v>17</v>
       </c>
-      <c r="P5" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3">
         <v>10</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1">
@@ -1010,54 +1020,54 @@
       <c r="C6" s="2">
         <v>0.13100000000000001</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="13">
         <v>0</v>
       </c>
       <c r="E6" s="2">
         <v>0.86899999999999999</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>-0.30000000000000027</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4">
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
         <v>3</v>
       </c>
-      <c r="L6" s="8">
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
         <v>6</v>
       </c>
-      <c r="N6" s="8">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4">
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
         <v>15</v>
       </c>
-      <c r="P6" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4">
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3">
         <v>9</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
@@ -1066,54 +1076,54 @@
       <c r="C7" s="2">
         <v>0.126</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="2">
         <v>0.874</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>4.0000000000000036</v>
       </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4">
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3">
         <v>2</v>
       </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
+      <c r="L7" s="7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
         <v>6</v>
       </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4">
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
         <v>16</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="7">
         <v>-1</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="Q7" s="3">
         <v>6</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1">
@@ -1122,54 +1132,54 @@
       <c r="C8" s="2">
         <v>0.21199999999999997</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="2">
         <v>0.78800000000000003</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>-0.30000000000000027</v>
       </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4">
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>17</v>
       </c>
-      <c r="L8" s="8">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
         <v>11</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="7">
         <v>-1</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="3">
         <v>22</v>
       </c>
-      <c r="P8" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4">
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>35</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="1">
@@ -1178,446 +1188,446 @@
       <c r="C9" s="2">
         <v>0.18300000000000005</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="2">
         <v>0.81699999999999995</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>0.8999999999999897</v>
       </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4">
-        <v>1</v>
-      </c>
-      <c r="L9" s="8">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4">
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="7">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>7</v>
       </c>
-      <c r="N9" s="8">
-        <v>1</v>
-      </c>
-      <c r="O9" s="4">
+      <c r="N9" s="7">
+        <v>1</v>
+      </c>
+      <c r="O9" s="3">
         <v>17</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="7">
         <v>3</v>
       </c>
-      <c r="Q9" s="4">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
+      <c r="Q9" s="3">
+        <v>0</v>
+      </c>
+      <c r="R9" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>5291</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>0.16500000000000004</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="13">
         <v>0</v>
       </c>
       <c r="E10" s="2">
         <v>0.83499999999999996</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>8.9999999999999964</v>
       </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
-        <v>0</v>
-      </c>
-      <c r="J10" s="8">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0</v>
-      </c>
-      <c r="L10" s="8">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4">
-        <v>1</v>
-      </c>
-      <c r="N10" s="8">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4">
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1</v>
+      </c>
+      <c r="N10" s="7">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>11</v>
       </c>
-      <c r="P10" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4">
-        <v>1</v>
-      </c>
-      <c r="R10" s="8">
+      <c r="P10" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>1</v>
+      </c>
+      <c r="R10" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>24203</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>0.15400000000000003</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="13">
         <v>0</v>
       </c>
       <c r="E11" s="2">
         <v>0.84599999999999997</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>1.0000000000000009</v>
       </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4">
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
         <v>8</v>
       </c>
-      <c r="L11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
+      <c r="L11" s="7">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
         <v>10</v>
       </c>
-      <c r="N11" s="8">
-        <v>1</v>
-      </c>
-      <c r="O11" s="4">
+      <c r="N11" s="7">
+        <v>1</v>
+      </c>
+      <c r="O11" s="3">
         <v>16</v>
       </c>
-      <c r="P11" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4">
+      <c r="P11" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
         <v>20</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>44354</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>0.18</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="13">
         <v>-2.5</v>
       </c>
       <c r="E12" s="2">
         <v>0.79500000000000004</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="8">
         <v>-0.50000000000000044</v>
       </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4">
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
         <v>6</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="7">
         <v>6</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="3">
         <v>20</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="7">
         <v>3</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M12" s="3">
         <v>15</v>
       </c>
-      <c r="N12" s="8">
-        <v>1</v>
-      </c>
-      <c r="O12" s="4">
+      <c r="N12" s="7">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3">
         <v>19</v>
       </c>
-      <c r="P12" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4">
+      <c r="P12" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
         <v>30</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="7">
         <v>-2</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>11524</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>0.11099999999999999</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="13">
         <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0.88900000000000001</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="8">
         <v>5.8000000000000052</v>
       </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4">
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
         <v>2</v>
       </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4">
+      <c r="L13" s="7">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
         <v>6</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="7">
         <v>-1</v>
       </c>
-      <c r="O13" s="4">
+      <c r="O13" s="3">
         <v>10</v>
       </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4">
+      <c r="P13" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
         <v>9</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>27615</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>0.13000000000000003</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="13">
         <v>-2.7</v>
       </c>
       <c r="E14" s="2">
         <v>0.84299999999999997</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="8">
         <v>0.30000000000000027</v>
       </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>9</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="7">
         <v>9</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="3">
         <v>4</v>
       </c>
-      <c r="L14" s="8">
-        <v>1</v>
-      </c>
-      <c r="M14" s="4">
+      <c r="L14" s="7">
+        <v>1</v>
+      </c>
+      <c r="M14" s="3">
         <v>14</v>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="7">
         <v>-1</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O14" s="3">
         <v>22</v>
       </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="4">
+      <c r="P14" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>19</v>
       </c>
-      <c r="R14" s="8">
+      <c r="R14" s="7">
         <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>11205</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>0.159</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="13">
         <v>-3.5</v>
       </c>
       <c r="E15" s="2">
         <v>0.80600000000000005</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>0.30000000000000027</v>
       </c>
-      <c r="G15" s="4">
-        <v>1</v>
-      </c>
-      <c r="H15" s="8">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4">
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
         <v>5</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="7">
         <v>5</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="3">
         <v>2</v>
       </c>
-      <c r="L15" s="8">
-        <v>1</v>
-      </c>
-      <c r="M15" s="4">
+      <c r="L15" s="7">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3">
         <v>4</v>
       </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4">
+      <c r="N15" s="7">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>20</v>
       </c>
-      <c r="P15" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="4">
-        <v>0</v>
-      </c>
-      <c r="R15" s="8">
+      <c r="P15" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>10013</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>0.16300000000000003</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="13">
         <v>0</v>
       </c>
       <c r="E16" s="2">
         <v>0.83699999999999997</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <v>0.30000000000000027</v>
       </c>
-      <c r="G16" s="4">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
-      <c r="J16" s="8">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4">
-        <v>1</v>
-      </c>
-      <c r="L16" s="8">
-        <v>0</v>
-      </c>
-      <c r="M16" s="4">
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
         <v>2</v>
       </c>
-      <c r="N16" s="8">
-        <v>0</v>
-      </c>
-      <c r="O16" s="4">
+      <c r="N16" s="7">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3">
         <v>22</v>
       </c>
-      <c r="P16" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="4">
-        <v>0</v>
-      </c>
-      <c r="R16" s="8">
+      <c r="P16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0</v>
+      </c>
+      <c r="R16" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="1">
@@ -1626,54 +1636,54 @@
       <c r="C17" s="2">
         <v>0.26</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="13">
         <v>0</v>
       </c>
       <c r="E17" s="2">
         <v>0.74</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>6.7999999999999954</v>
       </c>
-      <c r="G17" s="4">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
-        <v>1</v>
-      </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="4">
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1</v>
+      </c>
+      <c r="L17" s="7">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
         <v>3</v>
       </c>
-      <c r="N17" s="8">
-        <v>0</v>
-      </c>
-      <c r="O17" s="4">
+      <c r="N17" s="7">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3">
         <v>16</v>
       </c>
-      <c r="P17" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="4">
+      <c r="P17" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3">
         <v>7</v>
       </c>
-      <c r="R17" s="8">
+      <c r="R17" s="7">
         <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="1">
@@ -1682,54 +1692,54 @@
       <c r="C18" s="2">
         <v>0.13600000000000004</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="13">
         <v>-2</v>
       </c>
       <c r="E18" s="2">
         <v>0.84399999999999997</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <v>-0.10000000000000009</v>
       </c>
-      <c r="G18" s="4">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4">
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>5</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="7">
         <v>5</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="3">
         <v>2</v>
       </c>
-      <c r="L18" s="8">
-        <v>0</v>
-      </c>
-      <c r="M18" s="4">
+      <c r="L18" s="7">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>5</v>
       </c>
-      <c r="N18" s="8">
-        <v>0</v>
-      </c>
-      <c r="O18" s="4">
+      <c r="N18" s="7">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>21</v>
       </c>
-      <c r="P18" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="4">
+      <c r="P18" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="3">
         <v>21</v>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="1">
@@ -1738,54 +1748,54 @@
       <c r="C19" s="2">
         <v>0.17900000000000005</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="13">
         <v>0</v>
       </c>
       <c r="E19" s="2">
         <v>0.82099999999999995</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <v>-0.20000000000000018</v>
       </c>
-      <c r="G19" s="4">
-        <v>0</v>
-      </c>
-      <c r="H19" s="8">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4">
-        <v>0</v>
-      </c>
-      <c r="J19" s="8">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4">
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
         <v>13</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="7">
         <v>3</v>
       </c>
-      <c r="M19" s="4">
+      <c r="M19" s="3">
         <v>9</v>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="7">
         <v>2</v>
       </c>
-      <c r="O19" s="4">
+      <c r="O19" s="3">
         <v>27</v>
       </c>
-      <c r="P19" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="4">
+      <c r="P19" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="3">
         <v>26</v>
       </c>
-      <c r="R19" s="8">
+      <c r="R19" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="1">
@@ -1794,54 +1804,54 @@
       <c r="C20" s="2">
         <v>0.15500000000000003</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="13">
         <v>0</v>
       </c>
       <c r="E20" s="2">
         <v>0.84499999999999997</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="8">
         <v>-0.30000000000000027</v>
       </c>
-      <c r="G20" s="4">
-        <v>0</v>
-      </c>
-      <c r="H20" s="8">
-        <v>0</v>
-      </c>
-      <c r="I20" s="4">
-        <v>0</v>
-      </c>
-      <c r="J20" s="8">
-        <v>0</v>
-      </c>
-      <c r="K20" s="4">
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>72</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="7">
         <v>8</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M20" s="3">
         <v>11</v>
       </c>
-      <c r="N20" s="8">
+      <c r="N20" s="7">
         <v>-4</v>
       </c>
-      <c r="O20" s="4">
+      <c r="O20" s="3">
         <v>33</v>
       </c>
-      <c r="P20" s="8">
+      <c r="P20" s="7">
         <v>2</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="Q20" s="3">
         <v>93</v>
       </c>
-      <c r="R20" s="8">
+      <c r="R20" s="7">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="1">
@@ -1850,54 +1860,54 @@
       <c r="C21" s="2">
         <v>0.122</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="13">
         <v>0</v>
       </c>
       <c r="E21" s="2">
         <v>0.878</v>
       </c>
-      <c r="F21" s="9">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8">
-        <v>0</v>
-      </c>
-      <c r="I21" s="4">
-        <v>0</v>
-      </c>
-      <c r="J21" s="8">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4">
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="7">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>11</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="7">
         <v>3</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M21" s="3">
         <v>23</v>
       </c>
-      <c r="N21" s="8">
+      <c r="N21" s="7">
         <v>-3</v>
       </c>
-      <c r="O21" s="4">
+      <c r="O21" s="3">
         <v>23</v>
       </c>
-      <c r="P21" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4">
+      <c r="P21" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
         <v>17</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="7">
         <v>-2</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="1">
@@ -1906,54 +1916,54 @@
       <c r="C22" s="2">
         <v>0.17300000000000004</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="13">
         <v>0</v>
       </c>
       <c r="E22" s="2">
         <v>0.82699999999999996</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="8">
         <v>0.50000000000000044</v>
       </c>
-      <c r="G22" s="4">
-        <v>0</v>
-      </c>
-      <c r="H22" s="8">
-        <v>0</v>
-      </c>
-      <c r="I22" s="4">
-        <v>0</v>
-      </c>
-      <c r="J22" s="8">
-        <v>0</v>
-      </c>
-      <c r="K22" s="4">
-        <v>1</v>
-      </c>
-      <c r="L22" s="8">
-        <v>0</v>
-      </c>
-      <c r="M22" s="4">
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1</v>
+      </c>
+      <c r="L22" s="7">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
         <v>2</v>
       </c>
-      <c r="N22" s="8">
-        <v>0</v>
-      </c>
-      <c r="O22" s="4">
+      <c r="N22" s="7">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
         <v>10</v>
       </c>
-      <c r="P22" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="4">
+      <c r="P22" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="3">
         <v>2</v>
       </c>
-      <c r="R22" s="8">
+      <c r="R22" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="1">
@@ -1962,110 +1972,110 @@
       <c r="C23" s="2">
         <v>0.17000000000000004</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="13">
         <v>0</v>
       </c>
       <c r="E23" s="2">
         <v>0.83</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>10.499999999999998</v>
       </c>
-      <c r="G23" s="4">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4">
-        <v>0</v>
-      </c>
-      <c r="J23" s="8">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4">
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="7">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>3</v>
       </c>
-      <c r="L23" s="8">
-        <v>0</v>
-      </c>
-      <c r="M23" s="4">
+      <c r="L23" s="7">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>13</v>
       </c>
-      <c r="N23" s="8">
-        <v>1</v>
-      </c>
-      <c r="O23" s="4">
+      <c r="N23" s="7">
+        <v>1</v>
+      </c>
+      <c r="O23" s="3">
         <v>17</v>
       </c>
-      <c r="P23" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="4">
+      <c r="P23" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>24</v>
       </c>
-      <c r="R23" s="8">
+      <c r="R23" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="1">
         <v>12496</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>0.28099999999999997</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="13">
         <v>-3.7</v>
       </c>
       <c r="E24" s="2">
         <v>0.68200000000000005</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="8">
         <v>14.100000000000001</v>
       </c>
-      <c r="G24" s="4">
-        <v>1</v>
-      </c>
-      <c r="H24" s="8">
-        <v>1</v>
-      </c>
-      <c r="I24" s="4">
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
         <v>10</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="7">
         <v>10</v>
       </c>
-      <c r="K24" s="4">
-        <v>0</v>
-      </c>
-      <c r="L24" s="8">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4">
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>6</v>
       </c>
-      <c r="N24" s="8">
-        <v>0</v>
-      </c>
-      <c r="O24" s="4">
+      <c r="N24" s="7">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>8</v>
       </c>
-      <c r="P24" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="4">
-        <v>0</v>
-      </c>
-      <c r="R24" s="8">
+      <c r="P24" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="1">
@@ -2074,54 +2084,54 @@
       <c r="C25" s="2">
         <v>0.22599999999999998</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="13">
         <v>0</v>
       </c>
       <c r="E25" s="2">
         <v>0.77400000000000002</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="8">
         <v>-0.30000000000000027</v>
       </c>
-      <c r="G25" s="4">
-        <v>0</v>
-      </c>
-      <c r="H25" s="8">
-        <v>0</v>
-      </c>
-      <c r="I25" s="4">
-        <v>0</v>
-      </c>
-      <c r="J25" s="8">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4">
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="7">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
         <v>5</v>
       </c>
-      <c r="L25" s="8">
-        <v>1</v>
-      </c>
-      <c r="M25" s="4">
+      <c r="L25" s="7">
+        <v>1</v>
+      </c>
+      <c r="M25" s="3">
         <v>11</v>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="7">
         <v>-1</v>
       </c>
-      <c r="O25" s="4">
+      <c r="O25" s="3">
         <v>28</v>
       </c>
-      <c r="P25" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="4">
+      <c r="P25" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
         <v>7</v>
       </c>
-      <c r="R25" s="8">
+      <c r="R25" s="7">
         <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="1">
@@ -2130,54 +2140,54 @@
       <c r="C26" s="2">
         <v>0.15000000000000002</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="13">
         <v>0</v>
       </c>
       <c r="E26" s="2">
         <v>0.85</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="8">
         <v>4.2999999999999927</v>
       </c>
-      <c r="G26" s="4">
-        <v>0</v>
-      </c>
-      <c r="H26" s="8">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4">
-        <v>0</v>
-      </c>
-      <c r="J26" s="8">
-        <v>0</v>
-      </c>
-      <c r="K26" s="4">
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="7">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>9</v>
       </c>
-      <c r="L26" s="8">
-        <v>0</v>
-      </c>
-      <c r="M26" s="4">
+      <c r="L26" s="7">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>3</v>
       </c>
-      <c r="N26" s="8">
+      <c r="N26" s="7">
         <v>-1</v>
       </c>
-      <c r="O26" s="4">
+      <c r="O26" s="3">
         <v>15</v>
       </c>
-      <c r="P26" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4">
+      <c r="P26" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>5</v>
       </c>
-      <c r="R26" s="8">
+      <c r="R26" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="10" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="1">
@@ -2186,54 +2196,54 @@
       <c r="C27" s="2">
         <v>0.24299999999999999</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="13">
         <v>0</v>
       </c>
       <c r="E27" s="2">
         <v>0.75700000000000001</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="8">
         <v>-1.0000000000000009</v>
       </c>
-      <c r="G27" s="4">
-        <v>0</v>
-      </c>
-      <c r="H27" s="8">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4">
-        <v>0</v>
-      </c>
-      <c r="J27" s="8">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4">
-        <v>0</v>
-      </c>
-      <c r="L27" s="8">
-        <v>0</v>
-      </c>
-      <c r="M27" s="4">
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="7">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="7">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>5</v>
       </c>
-      <c r="N27" s="8">
-        <v>0</v>
-      </c>
-      <c r="O27" s="4">
+      <c r="N27" s="7">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>13</v>
       </c>
-      <c r="P27" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4">
+      <c r="P27" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>7</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R27" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="1">
@@ -2242,54 +2252,54 @@
       <c r="C28" s="2">
         <v>0.18500000000000005</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="13">
         <v>0</v>
       </c>
       <c r="E28" s="2">
         <v>0.81499999999999995</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="8">
         <v>10.7</v>
       </c>
-      <c r="G28" s="4">
-        <v>0</v>
-      </c>
-      <c r="H28" s="8">
-        <v>0</v>
-      </c>
-      <c r="I28" s="4">
-        <v>0</v>
-      </c>
-      <c r="J28" s="8">
-        <v>0</v>
-      </c>
-      <c r="K28" s="4">
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7">
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="7">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
         <v>3</v>
       </c>
-      <c r="L28" s="8">
-        <v>1</v>
-      </c>
-      <c r="M28" s="4">
+      <c r="L28" s="7">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3">
         <v>10</v>
       </c>
-      <c r="N28" s="8">
-        <v>0</v>
-      </c>
-      <c r="O28" s="4">
+      <c r="N28" s="7">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
         <v>23</v>
       </c>
-      <c r="P28" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="4">
+      <c r="P28" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
         <v>18</v>
       </c>
-      <c r="R28" s="8">
+      <c r="R28" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="10" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="1">
@@ -2298,54 +2308,54 @@
       <c r="C29" s="2">
         <v>0.21499999999999997</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="13">
         <v>0</v>
       </c>
       <c r="E29" s="2">
         <v>0.78500000000000003</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <v>-0.10000000000000009</v>
       </c>
-      <c r="G29" s="4">
-        <v>0</v>
-      </c>
-      <c r="H29" s="8">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4">
-        <v>0</v>
-      </c>
-      <c r="J29" s="8">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4">
-        <v>0</v>
-      </c>
-      <c r="L29" s="8">
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7">
         <v>-2</v>
       </c>
-      <c r="M29" s="4">
+      <c r="M29" s="3">
         <v>5</v>
       </c>
-      <c r="N29" s="8">
+      <c r="N29" s="7">
         <v>-1</v>
       </c>
-      <c r="O29" s="4">
+      <c r="O29" s="3">
         <v>19</v>
       </c>
-      <c r="P29" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="4">
+      <c r="P29" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>7</v>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B30" s="1">
@@ -2354,54 +2364,54 @@
       <c r="C30" s="2">
         <v>0.20399999999999996</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="13">
         <v>0</v>
       </c>
       <c r="E30" s="2">
         <v>0.79600000000000004</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="8">
         <v>9.5000000000000089</v>
       </c>
-      <c r="G30" s="4">
-        <v>0</v>
-      </c>
-      <c r="H30" s="8">
-        <v>0</v>
-      </c>
-      <c r="I30" s="4">
-        <v>0</v>
-      </c>
-      <c r="J30" s="8">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4">
-        <v>1</v>
-      </c>
-      <c r="L30" s="8">
-        <v>0</v>
-      </c>
-      <c r="M30" s="4">
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
+        <v>1</v>
+      </c>
+      <c r="L30" s="7">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
         <v>6</v>
       </c>
-      <c r="N30" s="8">
-        <v>0</v>
-      </c>
-      <c r="O30" s="4">
+      <c r="N30" s="7">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
         <v>15</v>
       </c>
-      <c r="P30" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="4">
+      <c r="P30" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
         <v>6</v>
       </c>
-      <c r="R30" s="8">
+      <c r="R30" s="7">
         <v>-3</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="10" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="1">
@@ -2410,85 +2420,88 @@
       <c r="C31" s="2">
         <v>0.22699999999999998</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="13">
         <v>0</v>
       </c>
       <c r="E31" s="2">
         <v>0.77300000000000002</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="8">
         <v>-5.8999999999999941</v>
       </c>
-      <c r="G31" s="4">
-        <v>0</v>
-      </c>
-      <c r="H31" s="8">
-        <v>0</v>
-      </c>
-      <c r="I31" s="4">
-        <v>0</v>
-      </c>
-      <c r="J31" s="8">
-        <v>0</v>
-      </c>
-      <c r="K31" s="4">
-        <v>0</v>
-      </c>
-      <c r="L31" s="8">
-        <v>0</v>
-      </c>
-      <c r="M31" s="4">
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="7">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
         <v>2</v>
       </c>
-      <c r="N31" s="8">
-        <v>0</v>
-      </c>
-      <c r="O31" s="4">
+      <c r="N31" s="7">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
         <v>14</v>
       </c>
-      <c r="P31" s="8">
+      <c r="P31" s="7">
         <v>-1</v>
       </c>
-      <c r="Q31" s="4">
-        <v>0</v>
-      </c>
-      <c r="R31" s="8">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
     </row>
     <row r="33" spans="13:14" x14ac:dyDescent="0.3">
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D31">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="greaterThan">
+  <conditionalFormatting sqref="F2:F31">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F31">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="15" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H31">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J31">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L31">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N31">
     <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -2496,7 +2509,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N31">
+  <conditionalFormatting sqref="P2:P31">
     <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -2504,7 +2517,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P31">
+  <conditionalFormatting sqref="R2:R31">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -2512,7 +2525,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R31">
+  <conditionalFormatting sqref="D2:D31">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/content/xls/NSO_p_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_p_regions_01.07.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Юлия\Desktop\ФД_2026\10.08.26\от Егора_итоговые файлы_25.08.26\Ответ_измен. ур.дбо_зеленым\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EE6535-41D8-40F2-AEDC-48397D482BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EDA8DC-7ADC-4C4F-B9D9-7AC1FA4DDD98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -276,7 +276,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -306,9 +306,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -320,7 +317,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="28">
     <dxf>
       <font>
         <color theme="9" tint="-0.499984740745262"/>
@@ -368,6 +365,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
     </dxf>
@@ -378,6 +385,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="9" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -394,6 +411,51 @@
     <dxf>
       <font>
         <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
       </font>
     </dxf>
   </dxfs>
@@ -707,86 +769,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8ED133E-911A-4285-ABEA-63C58E8165A8}">
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultRowHeight="14.8" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="17.44140625" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="18.109375" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.5546875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="16.5546875" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="19.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="13.33203125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="18.140625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="16.5703125" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="19.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1" collapsed="1"/>
     <col min="14" max="14" width="15" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1" collapsed="1"/>
     <col min="16" max="16" width="18" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="15.6640625" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="15.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="9.109375" collapsed="1"/>
+    <col min="17" max="17" width="15.7109375" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="15.7109375" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="9.140625" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="6" customFormat="1" ht="118.15" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:18" s="6" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="11" t="s">
         <v>46</v>
       </c>
       <c r="R1" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -796,7 +858,7 @@
       <c r="C2" s="2">
         <v>0.21199999999999997</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>0</v>
       </c>
       <c r="E2" s="2">
@@ -842,7 +904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -852,7 +914,7 @@
       <c r="C3" s="2">
         <v>0.24399999999999999</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>0</v>
       </c>
       <c r="E3" s="2">
@@ -898,7 +960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -908,7 +970,7 @@
       <c r="C4" s="2">
         <v>0.18400000000000005</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>0</v>
       </c>
       <c r="E4" s="2">
@@ -954,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>3</v>
       </c>
@@ -964,7 +1026,7 @@
       <c r="C5" s="2">
         <v>0.16700000000000004</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>0</v>
       </c>
       <c r="E5" s="2">
@@ -1010,7 +1072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1082,7 @@
       <c r="C6" s="2">
         <v>0.13100000000000001</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>0</v>
       </c>
       <c r="E6" s="2">
@@ -1066,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
@@ -1076,7 +1138,7 @@
       <c r="C7" s="2">
         <v>0.126</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>0</v>
       </c>
       <c r="E7" s="2">
@@ -1122,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
@@ -1132,7 +1194,7 @@
       <c r="C8" s="2">
         <v>0.21199999999999997</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>0</v>
       </c>
       <c r="E8" s="2">
@@ -1178,7 +1240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>7</v>
       </c>
@@ -1188,7 +1250,7 @@
       <c r="C9" s="2">
         <v>0.18300000000000005</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>0</v>
       </c>
       <c r="E9" s="2">
@@ -1234,17 +1296,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1">
         <v>5291</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="2">
         <v>0.16500000000000004</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <v>0</v>
       </c>
       <c r="E10" s="2">
@@ -1290,17 +1352,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1">
         <v>24203</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="2">
         <v>0.15400000000000003</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <v>0</v>
       </c>
       <c r="E11" s="2">
@@ -1346,17 +1408,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="1">
         <v>44354</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="2">
         <v>0.18</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <v>-2.5</v>
       </c>
       <c r="E12" s="2">
@@ -1402,17 +1464,17 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>11524</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="2">
         <v>0.11099999999999999</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <v>0</v>
       </c>
       <c r="E13" s="2">
@@ -1458,17 +1520,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>27615</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="2">
         <v>0.13000000000000003</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <v>-2.7</v>
       </c>
       <c r="E14" s="2">
@@ -1514,17 +1576,17 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="1">
         <v>11205</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="2">
         <v>0.159</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <v>-3.5</v>
       </c>
       <c r="E15" s="2">
@@ -1570,17 +1632,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>10013</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="2">
         <v>0.16300000000000003</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <v>0</v>
       </c>
       <c r="E16" s="2">
@@ -1626,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>15</v>
       </c>
@@ -1636,7 +1698,7 @@
       <c r="C17" s="2">
         <v>0.26</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="12">
         <v>0</v>
       </c>
       <c r="E17" s="2">
@@ -1682,7 +1744,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>16</v>
       </c>
@@ -1692,7 +1754,7 @@
       <c r="C18" s="2">
         <v>0.13600000000000004</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <v>-2</v>
       </c>
       <c r="E18" s="2">
@@ -1738,7 +1800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>17</v>
       </c>
@@ -1748,7 +1810,7 @@
       <c r="C19" s="2">
         <v>0.17900000000000005</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="12">
         <v>0</v>
       </c>
       <c r="E19" s="2">
@@ -1794,7 +1856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>18</v>
       </c>
@@ -1804,7 +1866,7 @@
       <c r="C20" s="2">
         <v>0.15500000000000003</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="12">
         <v>0</v>
       </c>
       <c r="E20" s="2">
@@ -1850,7 +1912,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>19</v>
       </c>
@@ -1860,7 +1922,7 @@
       <c r="C21" s="2">
         <v>0.122</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <v>0</v>
       </c>
       <c r="E21" s="2">
@@ -1906,7 +1968,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>20</v>
       </c>
@@ -1916,7 +1978,7 @@
       <c r="C22" s="2">
         <v>0.17300000000000004</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="12">
         <v>0</v>
       </c>
       <c r="E22" s="2">
@@ -1962,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>21</v>
       </c>
@@ -1972,7 +2034,7 @@
       <c r="C23" s="2">
         <v>0.17000000000000004</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="12">
         <v>0</v>
       </c>
       <c r="E23" s="2">
@@ -2018,7 +2080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>22</v>
       </c>
@@ -2028,7 +2090,7 @@
       <c r="C24" s="4">
         <v>0.28099999999999997</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <v>-3.7</v>
       </c>
       <c r="E24" s="2">
@@ -2074,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
@@ -2084,7 +2146,7 @@
       <c r="C25" s="2">
         <v>0.22599999999999998</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="12">
         <v>0</v>
       </c>
       <c r="E25" s="2">
@@ -2130,7 +2192,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>24</v>
       </c>
@@ -2140,7 +2202,7 @@
       <c r="C26" s="2">
         <v>0.15000000000000002</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="12">
         <v>0</v>
       </c>
       <c r="E26" s="2">
@@ -2186,7 +2248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>25</v>
       </c>
@@ -2196,7 +2258,7 @@
       <c r="C27" s="2">
         <v>0.24299999999999999</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="12">
         <v>0</v>
       </c>
       <c r="E27" s="2">
@@ -2242,7 +2304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>26</v>
       </c>
@@ -2252,7 +2314,7 @@
       <c r="C28" s="2">
         <v>0.18500000000000005</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="12">
         <v>0</v>
       </c>
       <c r="E28" s="2">
@@ -2298,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>27</v>
       </c>
@@ -2308,7 +2370,7 @@
       <c r="C29" s="2">
         <v>0.21499999999999997</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="12">
         <v>0</v>
       </c>
       <c r="E29" s="2">
@@ -2354,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>28</v>
       </c>
@@ -2364,7 +2426,7 @@
       <c r="C30" s="2">
         <v>0.20399999999999996</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="12">
         <v>0</v>
       </c>
       <c r="E30" s="2">
@@ -2410,7 +2472,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>29</v>
       </c>
@@ -2420,7 +2482,7 @@
       <c r="C31" s="2">
         <v>0.22699999999999998</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="12">
         <v>0</v>
       </c>
       <c r="E31" s="2">
@@ -2466,70 +2528,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
     </row>
-    <row r="33" spans="13:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F2:F31">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="lessThan">
+  <conditionalFormatting sqref="D2:D31">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F31">
+    <cfRule type="cellIs" dxfId="27" priority="14" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="15" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H31">
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J31">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="11" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L31">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="9" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N31">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P31">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="5" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R31">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D31">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
